--- a/source.xlsx
+++ b/source.xlsx
@@ -12,6 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tasks" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plans" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dashboards" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="charts" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chart_data" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1601,4 +1604,1086 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Аналітика документів</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>⬆️ id сторінки</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Заголовок дашборду</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Кількість колонок (2 або 3)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>dashboard_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_client</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Кількість документів з типами клієнтів</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>#4F7CFF</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>docs_dynamics</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Динаміка документів за 2026</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>#6C8AFF</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Кількість документів у розрізі систем</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>#4F7CFF</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>files_dynamics</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Динаміка обсягу файлів за 2026</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>#6C8AFF</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Обсяг файлів за 2026 у розрізі процесів</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>#4F7CFF</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>deleted_gb</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Видалено GB по місяцях</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>#EF4444</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>⬆️ = id з dashboards</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Унікальний id графіка</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>bar / line / horizontal_bar</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>HEX-колір</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Порядок (1,2,3...)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>chart_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_client</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ФО</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>126827084</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>+3.4 тис</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_client</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ЮО</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>3248988</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>+90 тис</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_client</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>СПД</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2260084</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>+59 тис</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_client</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Самозайняті</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>14259</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_client</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6388</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_client</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Представництва ЮО</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>4369</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_client</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Держ.установи</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>docs_dynamics</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1731828</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>docs_dynamics</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1785237</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>docs_dynamics</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1874229</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>IOS</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>980000</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CIB_SP</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>850000</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>780000</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>UCP</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>650000</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>LKP</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>420000</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>DIGITAL</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>380000</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>320000</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>BWM</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>280000</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>EPA</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>CLIENTBANK</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>CNRP</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SHRP</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>95000</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>DHA</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>docs_by_system</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SIRIUS</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>files_dynamics</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>660</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>files_dynamics</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>761</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>files_dynamics</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>892</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Кредитування фізичних</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Кредитування юридичних</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Картки фізичних</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Конверсія картка</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Авторизація</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Депозитні операції</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Зарплатний проєкт</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Знос бухгалтерія</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Каса</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Документообіг</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>files_by_process</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Валютні операції</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>deleted_gb</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Січ.26</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>823</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>deleted_gb</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Лют.26</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>557</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>deleted_gb</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Бер.26</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>⬆️ = id з charts</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Підпис (вісь X)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Значення (число)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Додатковий текст (необов'язково)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/source.xlsx
+++ b/source.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://api.dicebear.com/7.x/avataaars/svg?seed=Sasha&amp;backgroundColor=b6e3f4</t>
+          <t>avatar.png</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_AAD9102B92403543672C91DDF4EDF838E89B8350" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22516C41-D748-481F-BD52-9A4744C8A5B1}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_9E7F102B92403543675C9AC5FCECC042E87F79C6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{899D7104-5411-4B59-9F9B-4D76674E862F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="profile" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="191">
   <si>
     <t>key</t>
   </si>
@@ -334,34 +334,43 @@
     <t>business</t>
   </si>
   <si>
+    <t>Презентувати наш успішний customer-case з nuxeo на конференції HYLAND</t>
+  </si>
+  <si>
+    <t>tech</t>
+  </si>
+  <si>
+    <t>Сервіс міграції документів з колекції mongodb</t>
+  </si>
+  <si>
     <t>Видалення папки /Clients та AGREEMENT_DOCUMENTS на stage</t>
   </si>
   <si>
-    <t>tech</t>
-  </si>
-  <si>
-    <t>Сервіс міграції документів з колекції mongodb</t>
-  </si>
-  <si>
-    <t>Презентувати наш успішний customer-case з nuxeo на конференції HYLAND</t>
-  </si>
-  <si>
     <t>NUXEO 2019 -&gt; NUXEO 2023 | Реліз в PROD</t>
   </si>
   <si>
-    <t>DRP план для DC4</t>
-  </si>
-  <si>
-    <t>Інтеграція з новими партнерами</t>
-  </si>
-  <si>
-    <t>Розширення функціоналу ЦОП</t>
-  </si>
-  <si>
-    <t>Рефакторинг Easy Entry BOT</t>
-  </si>
-  <si>
-    <t>Оптимізація Entity block_list</t>
+    <t>Міграція /kofola/v1/accounts/by-filters -&gt; /kofola/v2/accounts/by-filters</t>
+  </si>
+  <si>
+    <t>PROD | Ретраї по втановленню курсів</t>
+  </si>
+  <si>
+    <t>PROD [URRO-12744]: |Customer Growth Tribe| (PUMB Online - ЦОП) Врахування типу документа при пошуку існуючих клієнтів</t>
+  </si>
+  <si>
+    <t>PROD [URRO-12783]: MMF-11698 |Easy Entry| ЮО/Оновлення логіки повернення блоку black_list_summary при створенні анкети потенційної ЮО</t>
+  </si>
+  <si>
+    <t>PROD [URRO-13007]: MMF-10188| |Customer Growth Tribe| [PUMB Online - ЦОП] Збагачення потенційного клієнта ідентифікаційними даними</t>
+  </si>
+  <si>
+    <t>PROD [URRO-12784]: MMF-11698 |Easy Entry| ФО/Оновлення логіки повернення блоку black_list_summary при створенні анкети технічного ФО</t>
+  </si>
+  <si>
+    <t>PROD [URRO-12782]: MMF-11698 |Easy Entry| ФОП/Оновлення логіки повернення блоку black_list_summary при створенні анкети потенційного ФОП</t>
+  </si>
+  <si>
+    <t>PROD [URRO-12881]: |Platform Tribe| Налаштування процесу передачі нових типів зв'язків в ЄКБ</t>
   </si>
   <si>
     <t>business / tech</t>
@@ -460,6 +469,9 @@
     <t>chart_id</t>
   </si>
   <si>
+    <t>prev_value</t>
+  </si>
+  <si>
     <t>ФО</t>
   </si>
   <si>
@@ -592,10 +604,13 @@
     <t>Підпис (вісь X)</t>
   </si>
   <si>
-    <t>Значення (число)</t>
-  </si>
-  <si>
-    <t>Додатковий текст (необов'язково)</t>
+    <t>Значення</t>
+  </si>
+  <si>
+    <t>Попереднє значення (для дельти)</t>
+  </si>
+  <si>
+    <t>Доп. текст</t>
   </si>
 </sst>
 </file>
@@ -679,8 +694,8 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1227,7 +1242,9 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>37</v>
       </c>
@@ -1451,7 +1468,7 @@
       <c r="B15" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" t="s">
         <v>67</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -1644,7 +1661,7 @@
       <c r="D3" s="2">
         <v>587</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1672,7 +1689,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1718,7 +1735,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>101</v>
@@ -1737,7 +1754,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>99</v>
@@ -1751,7 +1768,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>104</v>
@@ -1762,7 +1779,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>105</v>
@@ -1791,14 +1808,47 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>109</v>
+      <c r="B14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1824,15 +1874,15 @@
         <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C2" s="2">
         <v>3</v>
@@ -1840,13 +1890,13 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1866,7 +1916,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
@@ -1881,24 +1931,24 @@
         <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -1906,19 +1956,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
@@ -1926,19 +1976,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
@@ -1946,19 +1996,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="F5" s="2">
         <v>4</v>
@@ -1966,19 +2016,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
@@ -1986,19 +2036,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F7" s="2">
         <v>6</v>
@@ -2006,22 +2056,22 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2031,551 +2081,612 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C2" s="2">
         <v>126827084</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C3" s="2">
         <v>3248988</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C4" s="2">
         <v>2260084</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C5" s="2">
         <v>14259</v>
       </c>
       <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C6" s="2">
         <v>6388</v>
       </c>
       <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C7" s="2">
         <v>4369</v>
       </c>
       <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C8" s="2">
         <v>37</v>
       </c>
       <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C9" s="2">
         <v>1731828</v>
       </c>
       <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C10" s="2">
         <v>1785237</v>
       </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="D10" s="2">
+        <v>1731828</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C11" s="2">
         <v>1874229</v>
       </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="D11" s="2">
+        <v>1785237</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2">
         <v>980000</v>
       </c>
       <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2">
         <v>850000</v>
       </c>
       <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2">
         <v>780000</v>
       </c>
       <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C15" s="2">
         <v>650000</v>
       </c>
       <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C16" s="2">
         <v>420000</v>
       </c>
       <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C17" s="2">
         <v>380000</v>
       </c>
       <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C18" s="2">
         <v>320000</v>
       </c>
       <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C19" s="2">
         <v>280000</v>
       </c>
       <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2">
         <v>210000</v>
       </c>
       <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C21" s="2">
         <v>180000</v>
       </c>
       <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2">
         <v>150000</v>
       </c>
       <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2">
         <v>120000</v>
       </c>
       <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2">
         <v>95000</v>
       </c>
       <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C25" s="2">
         <v>80000</v>
       </c>
       <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C26" s="2">
         <v>60000</v>
       </c>
       <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C27" s="2">
         <v>660</v>
       </c>
       <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C28" s="2">
         <v>761</v>
       </c>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="D28" s="2">
+        <v>660</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C29" s="2">
         <v>892</v>
       </c>
-      <c r="D29" s="2"/>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="D29" s="2">
+        <v>761</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C30" s="2">
         <v>1064</v>
       </c>
       <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C31" s="2">
         <v>444</v>
       </c>
       <c r="D31" s="2"/>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2">
         <v>169</v>
       </c>
       <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2">
         <v>92</v>
       </c>
       <c r="D33" s="2"/>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C34" s="2">
         <v>78</v>
       </c>
       <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C35" s="2">
         <v>66</v>
       </c>
       <c r="D35" s="2"/>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C36" s="2">
         <v>56</v>
       </c>
       <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C37" s="2">
         <v>32</v>
       </c>
       <c r="D37" s="2"/>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C38" s="2">
         <v>31</v>
       </c>
       <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C39" s="2">
         <v>28</v>
       </c>
       <c r="D39" s="2"/>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C40" s="2">
         <v>27</v>
       </c>
       <c r="D40" s="2"/>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C41" s="2">
         <v>823</v>
       </c>
       <c r="D41" s="2"/>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C42" s="2">
         <v>557</v>
       </c>
-      <c r="D42" s="2"/>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="D42" s="2">
+        <v>823</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C43" s="2">
         <v>223</v>
       </c>
-      <c r="D43" s="2"/>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="D43" s="2">
+        <v>557</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_9E7F102B92403543675C9AC5FCECC042E87F79C6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{899D7104-5411-4B59-9F9B-4D76674E862F}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_396E1F94D8E956806DA553F2870313D70BCCA1E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA8E470A-29AB-4B09-849C-ECAA771E463D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="profile" sheetId="1" r:id="rId1"/>
-    <sheet name="projects" sheetId="2" r:id="rId2"/>
-    <sheet name="tasks" sheetId="3" r:id="rId3"/>
-    <sheet name="metrics" sheetId="4" r:id="rId4"/>
-    <sheet name="plans" sheetId="5" r:id="rId5"/>
-    <sheet name="dashboards" sheetId="6" r:id="rId6"/>
-    <sheet name="charts" sheetId="7" r:id="rId7"/>
-    <sheet name="chart_data" sheetId="8" r:id="rId8"/>
+    <sheet name="summary" sheetId="1" r:id="rId1"/>
+    <sheet name="profile" sheetId="2" r:id="rId2"/>
+    <sheet name="projects" sheetId="3" r:id="rId3"/>
+    <sheet name="tasks" sheetId="4" r:id="rId4"/>
+    <sheet name="metrics" sheetId="5" r:id="rId5"/>
+    <sheet name="plans" sheetId="6" r:id="rId6"/>
+    <sheet name="dashboards" sheetId="7" r:id="rId7"/>
+    <sheet name="charts" sheetId="8" r:id="rId8"/>
+    <sheet name="chart_data" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="180">
   <si>
     <t>key</t>
   </si>
@@ -46,6 +47,42 @@
     <t>value</t>
   </si>
   <si>
+    <t>period_from</t>
+  </si>
+  <si>
+    <t>period_to</t>
+  </si>
+  <si>
+    <t>total_processes</t>
+  </si>
+  <si>
+    <t>new_processes</t>
+  </si>
+  <si>
+    <t>total_doc_types</t>
+  </si>
+  <si>
+    <t>new_doc_types</t>
+  </si>
+  <si>
+    <t>+1</t>
+  </si>
+  <si>
+    <t>done_business</t>
+  </si>
+  <si>
+    <t>done_tech</t>
+  </si>
+  <si>
+    <t>will_present</t>
+  </si>
+  <si>
+    <t>⬆️ Ключ</t>
+  </si>
+  <si>
+    <t>Значення</t>
+  </si>
+  <si>
     <t>password</t>
   </si>
   <si>
@@ -175,24 +212,12 @@
     <t>Успішне проведення тестування на DC4</t>
   </si>
   <si>
-    <t>EA-986</t>
-  </si>
-  <si>
-    <t>Виправлення невалідно мігрованих документів</t>
-  </si>
-  <si>
     <t>EA-1043</t>
   </si>
   <si>
     <t>Розбір проблеми з індексацією elastic</t>
   </si>
   <si>
-    <t>EA-971</t>
-  </si>
-  <si>
-    <t>Fulltest elastic + mongo removal</t>
-  </si>
-  <si>
     <t>EA-1066</t>
   </si>
   <si>
@@ -211,31 +236,13 @@
     <t>in-progress</t>
   </si>
   <si>
-    <t>EA-1027</t>
-  </si>
-  <si>
-    <t>Копіювання аудиту 2019-&gt;2023</t>
-  </si>
-  <si>
-    <t>EA-962</t>
-  </si>
-  <si>
-    <t>Налаштування PROD NUXEO 2023</t>
-  </si>
-  <si>
     <t>EA-1032</t>
   </si>
   <si>
-    <t>Міграція бінарів прод 2023</t>
-  </si>
-  <si>
-    <t>NUXEO 2019 → NUXEO 2023 | Підготовка до релізу в PROD</t>
-  </si>
-  <si>
-    <t>EA-1067</t>
-  </si>
-  <si>
-    <t>Ревью + узгодження плану дій щодо міграції 2023</t>
+    <t>MIGRATION | Міграція бінарів прод 2023</t>
+  </si>
+  <si>
+    <t>MIGRATION | Підготовка до релізу в PROD</t>
   </si>
   <si>
     <t>TASKS</t>
@@ -244,7 +251,7 @@
     <t>URRO-13007</t>
   </si>
   <si>
-    <t>MMF-10188| |Customer Growth Tribe| [PUMB Online - ЦОП] Збагачення потенційного клієнта ідентифікаційними даними</t>
+    <t>Збагачення потенційного клієнта ідентифікаційними даними</t>
   </si>
   <si>
     <t>URRO-13003</t>
@@ -253,28 +260,10 @@
     <t>Міграція на нові методи з BUS</t>
   </si>
   <si>
-    <t>URRO-12881</t>
-  </si>
-  <si>
-    <t>|Platform Tribe| Налаштування процесу передачі нових типів зв'язків в ЄКБ</t>
-  </si>
-  <si>
     <t>URRO-12839</t>
   </si>
   <si>
-    <t>TEST/STAGE [URRO-12789]: |Eurointegration Tribe| Ретраї по встановленню курсів</t>
-  </si>
-  <si>
-    <t>URRO-12744</t>
-  </si>
-  <si>
-    <t>Врахування типу документа при пошуку існуючих клієнтів</t>
-  </si>
-  <si>
-    <t>URRO-12782</t>
-  </si>
-  <si>
-    <t>MMF-11698 |Easy Entry|ФОП/Оновлення логіки повернення блоку black_list_summary при створенні анкети потенційного ФОП</t>
+    <t>Ретраї по встановленню курсів</t>
   </si>
   <si>
     <t>⬆️ = id з projects</t>
@@ -313,7 +302,7 @@
     <t>Нові типи документів</t>
   </si>
   <si>
-    <t>+1</t>
+    <t>-1</t>
   </si>
   <si>
     <t>Підпис метрики</t>
@@ -340,37 +329,19 @@
     <t>tech</t>
   </si>
   <si>
-    <t>Сервіс міграції документів з колекції mongodb</t>
-  </si>
-  <si>
     <t>Видалення папки /Clients та AGREEMENT_DOCUMENTS на stage</t>
   </si>
   <si>
-    <t>NUXEO 2019 -&gt; NUXEO 2023 | Реліз в PROD</t>
-  </si>
-  <si>
-    <t>Міграція /kofola/v1/accounts/by-filters -&gt; /kofola/v2/accounts/by-filters</t>
+    <t>MIGRATION | Реліз в PROD</t>
+  </si>
+  <si>
+    <t>PROD | Міграція /kofola/v1/accounts/by-filters -&gt; /kofola/v2/accounts/by-filters</t>
   </si>
   <si>
     <t>PROD | Ретраї по втановленню курсів</t>
   </si>
   <si>
-    <t>PROD [URRO-12744]: |Customer Growth Tribe| (PUMB Online - ЦОП) Врахування типу документа при пошуку існуючих клієнтів</t>
-  </si>
-  <si>
-    <t>PROD [URRO-12783]: MMF-11698 |Easy Entry| ЮО/Оновлення логіки повернення блоку black_list_summary при створенні анкети потенційної ЮО</t>
-  </si>
-  <si>
-    <t>PROD [URRO-13007]: MMF-10188| |Customer Growth Tribe| [PUMB Online - ЦОП] Збагачення потенційного клієнта ідентифікаційними даними</t>
-  </si>
-  <si>
-    <t>PROD [URRO-12784]: MMF-11698 |Easy Entry| ФО/Оновлення логіки повернення блоку black_list_summary при створенні анкети технічного ФО</t>
-  </si>
-  <si>
-    <t>PROD [URRO-12782]: MMF-11698 |Easy Entry| ФОП/Оновлення логіки повернення блоку black_list_summary при створенні анкети потенційного ФОП</t>
-  </si>
-  <si>
-    <t>PROD [URRO-12881]: |Platform Tribe| Налаштування процесу передачі нових типів зв'язків в ЄКБ</t>
+    <t>PROD | Збагачення потенційного клієнта ідентифікаційними даними</t>
   </si>
   <si>
     <t>business / tech</t>
@@ -602,9 +573,6 @@
   </si>
   <si>
     <t>Підпис (вісь X)</t>
-  </si>
-  <si>
-    <t>Значення</t>
   </si>
   <si>
     <t>Попереднє значення (для дельти)</t>
@@ -687,7 +655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -695,6 +663,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -998,6 +967,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5">
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1015,47 +1086,47 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3"/>
     </row>
@@ -1064,8 +1135,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1074,36 +1145,36 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D2" s="2">
         <v>72</v>
@@ -1120,13 +1191,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -1143,25 +1214,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1169,9 +1240,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F21"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1183,39 +1254,39 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -1223,19 +1294,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F3" s="2">
         <v>100</v>
@@ -1243,19 +1314,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F4" s="2">
         <v>100</v>
@@ -1263,19 +1334,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2">
         <v>100</v>
@@ -1283,19 +1354,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2">
         <v>100</v>
@@ -1303,39 +1374,39 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F7" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F8" s="2">
         <v>100</v>
@@ -1343,262 +1414,102 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F9" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>68</v>
+      </c>
+      <c r="C10" t="s">
+        <v>69</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F10" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1606,8 +1517,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1616,70 +1527,70 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D2" s="2">
         <v>148</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D3" s="2">
         <v>587</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>91</v>
+      <c r="E3" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1687,9 +1598,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C14"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1699,156 +1610,90 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>112</v>
+      <c r="A8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1856,8 +1701,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1868,21 +1713,21 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C2" s="2">
         <v>3</v>
@@ -1890,13 +1735,13 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1904,8 +1749,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1916,39 +1761,39 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -1956,19 +1801,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
@@ -1976,19 +1821,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
@@ -1996,19 +1841,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F5" s="2">
         <v>4</v>
@@ -2016,19 +1861,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
@@ -2036,19 +1881,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F7" s="2">
         <v>6</v>
@@ -2056,22 +1901,22 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2079,8 +1924,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2093,72 +1938,72 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C2" s="2">
         <v>126827084</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C3" s="2">
         <v>3248988</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C4" s="2">
         <v>2260084</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C5" s="2">
         <v>14259</v>
@@ -2168,10 +2013,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C6" s="2">
         <v>6388</v>
@@ -2181,10 +2026,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C7" s="2">
         <v>4369</v>
@@ -2194,10 +2039,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C8" s="2">
         <v>37</v>
@@ -2207,10 +2052,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C9" s="2">
         <v>1731828</v>
@@ -2220,10 +2065,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2">
         <v>1785237</v>
@@ -2235,10 +2080,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2">
         <v>1874229</v>
@@ -2250,10 +2095,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2">
         <v>980000</v>
@@ -2263,10 +2108,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C13" s="2">
         <v>850000</v>
@@ -2276,10 +2121,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C14" s="2">
         <v>780000</v>
@@ -2289,10 +2134,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C15" s="2">
         <v>650000</v>
@@ -2302,10 +2147,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C16" s="2">
         <v>420000</v>
@@ -2315,10 +2160,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2">
         <v>380000</v>
@@ -2328,10 +2173,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C18" s="2">
         <v>320000</v>
@@ -2341,10 +2186,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2">
         <v>280000</v>
@@ -2354,10 +2199,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2">
         <v>210000</v>
@@ -2367,10 +2212,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2">
         <v>180000</v>
@@ -2380,10 +2225,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C22" s="2">
         <v>150000</v>
@@ -2393,10 +2238,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C23" s="2">
         <v>120000</v>
@@ -2406,10 +2251,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C24" s="2">
         <v>95000</v>
@@ -2419,10 +2264,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2">
         <v>80000</v>
@@ -2432,10 +2277,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C26" s="2">
         <v>60000</v>
@@ -2445,10 +2290,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C27" s="2">
         <v>660</v>
@@ -2458,10 +2303,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C28" s="2">
         <v>761</v>
@@ -2473,10 +2318,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C29" s="2">
         <v>892</v>
@@ -2488,10 +2333,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C30" s="2">
         <v>1064</v>
@@ -2501,10 +2346,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C31" s="2">
         <v>444</v>
@@ -2514,10 +2359,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C32" s="2">
         <v>169</v>
@@ -2527,10 +2372,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C33" s="2">
         <v>92</v>
@@ -2540,10 +2385,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C34" s="2">
         <v>78</v>
@@ -2553,10 +2398,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C35" s="2">
         <v>66</v>
@@ -2566,10 +2411,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C36" s="2">
         <v>56</v>
@@ -2579,10 +2424,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C37" s="2">
         <v>32</v>
@@ -2592,10 +2437,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C38" s="2">
         <v>31</v>
@@ -2605,10 +2450,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C39" s="2">
         <v>28</v>
@@ -2618,10 +2463,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C40" s="2">
         <v>27</v>
@@ -2631,10 +2476,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C41" s="2">
         <v>823</v>
@@ -2644,10 +2489,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C42" s="2">
         <v>557</v>
@@ -2659,10 +2504,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C43" s="2">
         <v>223</v>
@@ -2674,19 +2519,19 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/source.xlsx
+++ b/source.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_396E1F94D8E956806DA553F2870313D70BCCA1E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA8E470A-29AB-4B09-849C-ECAA771E463D}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="11_396E1F94D8E956806DA553F2870313D70BCCA1E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02351634-21BB-4642-BA42-4005555B1DDE}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="179">
   <si>
     <t>key</t>
   </si>
@@ -293,16 +293,13 @@
     <t>BUSINESS</t>
   </si>
   <si>
-    <t>Нові процеси</t>
+    <t>Процеси</t>
   </si>
   <si>
     <t>+0</t>
   </si>
   <si>
-    <t>Нові типи документів</t>
-  </si>
-  <si>
-    <t>-1</t>
+    <t>Типи документів</t>
   </si>
   <si>
     <t>Підпис метрики</t>
@@ -446,21 +443,12 @@
     <t>ФО</t>
   </si>
   <si>
-    <t>+3.4 тис</t>
-  </si>
-  <si>
     <t>ЮО</t>
   </si>
   <si>
-    <t>+90 тис</t>
-  </si>
-  <si>
     <t>СПД</t>
   </si>
   <si>
-    <t>+59 тис</t>
-  </si>
-  <si>
     <t>Самозайняті</t>
   </si>
   <si>
@@ -482,91 +470,100 @@
     <t>2026-03</t>
   </si>
   <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>RBS</t>
+  </si>
+  <si>
     <t>IOS</t>
   </si>
   <si>
-    <t>CIB_SP</t>
-  </si>
-  <si>
-    <t>Android</t>
+    <t>CID_SF</t>
+  </si>
+  <si>
+    <t>ANDROID</t>
+  </si>
+  <si>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>LUI</t>
   </si>
   <si>
     <t>UCP</t>
   </si>
   <si>
-    <t>LKP</t>
-  </si>
-  <si>
     <t>DIGITAL</t>
   </si>
   <si>
-    <t>FW</t>
+    <t>PAYHUB</t>
   </si>
   <si>
     <t>BWM</t>
   </si>
   <si>
-    <t>EPA</t>
-  </si>
-  <si>
-    <t>CLIENTBANK</t>
+    <t>CBF</t>
+  </si>
+  <si>
+    <t>RPA</t>
+  </si>
+  <si>
+    <t>CLIENT_BANK</t>
   </si>
   <si>
     <t>CAMS</t>
   </si>
   <si>
-    <t>CNRP</t>
-  </si>
-  <si>
-    <t>SHRP</t>
-  </si>
-  <si>
-    <t>DHA</t>
+    <t>CNB</t>
+  </si>
+  <si>
+    <t>SHAREPOINT</t>
+  </si>
+  <si>
+    <t>DIIA</t>
   </si>
   <si>
     <t>SIRIUS</t>
   </si>
   <si>
-    <t>Кредитування фізичних</t>
-  </si>
-  <si>
-    <t>Кредитування юридичних</t>
-  </si>
-  <si>
-    <t>Картки фізичних</t>
-  </si>
-  <si>
-    <t>Конверсія картка</t>
-  </si>
-  <si>
-    <t>Авторизація</t>
-  </si>
-  <si>
-    <t>Депозитні операції</t>
-  </si>
-  <si>
-    <t>Зарплатний проєкт</t>
-  </si>
-  <si>
-    <t>Знос бухгалтерія</t>
-  </si>
-  <si>
-    <t>Каса</t>
-  </si>
-  <si>
-    <t>Документообіг</t>
-  </si>
-  <si>
-    <t>Валютні операції</t>
-  </si>
-  <si>
-    <t>Січ.26</t>
-  </si>
-  <si>
-    <t>Лют.26</t>
-  </si>
-  <si>
-    <t>Бер.26</t>
+    <t>Відеоверифікація</t>
+  </si>
+  <si>
+    <t>Ідентифікація</t>
+  </si>
+  <si>
+    <t>Відкриття рахунку</t>
+  </si>
+  <si>
+    <t>Кредитна картка</t>
+  </si>
+  <si>
+    <t>Споживчий кредит GP</t>
+  </si>
+  <si>
+    <t>Актуалізація</t>
+  </si>
+  <si>
+    <t>Переідентифікація</t>
+  </si>
+  <si>
+    <t>Зміна послуг в пакеті</t>
+  </si>
+  <si>
+    <t>Express_POS_SF</t>
+  </si>
+  <si>
+    <t>Single_Entry</t>
+  </si>
+  <si>
+    <t>Підтвердження джерел надходження коштів</t>
+  </si>
+  <si>
+    <t>Торговий еквайринг</t>
   </si>
   <si>
     <t>⬆️ = id з charts</t>
@@ -655,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -665,6 +662,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1035,7 +1033,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1043,7 +1041,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2">
-        <v>4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1572,8 +1570,8 @@
       <c r="D3" s="2">
         <v>587</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>87</v>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1584,13 +1582,13 @@
         <v>76</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1613,10 +1611,10 @@
         <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1624,10 +1622,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1635,10 +1633,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1646,10 +1644,10 @@
         <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1657,10 +1655,10 @@
         <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1668,10 +1666,10 @@
         <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1679,10 +1677,10 @@
         <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1690,10 +1688,10 @@
         <v>75</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1719,15 +1717,15 @@
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="C2" s="2">
         <v>3</v>
@@ -1735,13 +1733,13 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1761,7 +1759,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
@@ -1770,30 +1768,30 @@
         <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -1801,19 +1799,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
@@ -1821,19 +1819,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
@@ -1841,19 +1839,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F5" s="2">
         <v>4</v>
@@ -1861,19 +1859,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="D6" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
@@ -1881,19 +1879,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="F7" s="2">
         <v>6</v>
@@ -1901,22 +1899,22 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1926,7 +1924,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1938,7 +1936,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>81</v>
@@ -1947,7 +1945,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>82</v>
@@ -1955,583 +1953,955 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" s="2">
+        <v>133</v>
+      </c>
+      <c r="C2">
+        <v>130337849</v>
+      </c>
+      <c r="D2" s="2">
         <v>126827084</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
-        <v>135</v>
+      <c r="E2" s="2">
+        <f>C2-D2</f>
+        <v>3510765</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" s="2">
+        <v>134</v>
+      </c>
+      <c r="C3">
+        <v>3362927</v>
+      </c>
+      <c r="D3" s="2">
         <v>3248988</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>137</v>
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E53" si="0">C3-D3</f>
+        <v>113939</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="2">
+        <v>135</v>
+      </c>
+      <c r="C4">
+        <v>2333833</v>
+      </c>
+      <c r="D4" s="2">
         <v>2260084</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>139</v>
+      <c r="E4" s="2">
+        <f t="shared" si="0"/>
+        <v>73749</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="2">
+        <v>136</v>
+      </c>
+      <c r="C5">
+        <v>14238</v>
+      </c>
+      <c r="D5" s="2">
         <v>14259</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>-21</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="2">
+        <v>137</v>
+      </c>
+      <c r="C6">
+        <v>6471</v>
+      </c>
+      <c r="D6" s="2">
         <v>6388</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="2">
+        <v>138</v>
+      </c>
+      <c r="C7">
+        <v>4547</v>
+      </c>
+      <c r="D7" s="2">
         <v>4369</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="2">
+        <v>139</v>
+      </c>
+      <c r="C8">
         <v>37</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="D8" s="2">
+        <v>37</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1731828</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="C9">
+        <v>1731893</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="0"/>
+        <v>1731893</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1785237</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1731828</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="C10">
+        <v>1785359</v>
+      </c>
+      <c r="D10">
+        <v>1731893</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" si="0"/>
+        <v>53466</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1874229</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1785237</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="C11">
+        <v>2531658</v>
+      </c>
+      <c r="D11">
+        <v>1785359</v>
+      </c>
+      <c r="E11" s="2">
+        <f t="shared" si="0"/>
+        <v>746299</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="2">
-        <v>980000</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="C12">
+        <v>2143981</v>
+      </c>
+      <c r="D12">
+        <v>2531658</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>-387677</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" s="2">
-        <v>850000</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C13">
+        <v>897399</v>
+      </c>
+      <c r="D13">
+        <v>2143981</v>
+      </c>
+      <c r="E13" s="2">
+        <f t="shared" si="0"/>
+        <v>-1246582</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="2">
-        <v>780000</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+        <v>145</v>
+      </c>
+      <c r="C14">
+        <v>73945958</v>
+      </c>
+      <c r="D14" s="2">
+        <v>73042000</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="0"/>
+        <v>903958</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="2">
-        <v>650000</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="C15">
+        <v>23240317</v>
+      </c>
+      <c r="D15" s="2">
+        <v>22187000</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="0"/>
+        <v>1053317</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="2">
-        <v>420000</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="C16">
+        <v>15038162</v>
+      </c>
+      <c r="D16" s="2">
+        <v>15021000</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="0"/>
+        <v>17162</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C17" s="2">
-        <v>380000</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C17">
+        <v>13788865</v>
+      </c>
+      <c r="D17" s="2">
+        <v>12443000</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="0"/>
+        <v>1345865</v>
+      </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C18" s="2">
-        <v>320000</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="C18">
+        <v>5685057</v>
+      </c>
+      <c r="D18" s="2">
+        <v>5595000</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="0"/>
+        <v>90057</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="2">
-        <v>280000</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="C19">
+        <v>1560589</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1369000</v>
+      </c>
+      <c r="E19" s="2">
+        <f t="shared" si="0"/>
+        <v>191589</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C20" s="2">
-        <v>210000</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="C20">
+        <v>1192877</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1191000</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="0"/>
+        <v>1877</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C21" s="2">
-        <v>180000</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="C21">
+        <v>393048</v>
+      </c>
+      <c r="D21" s="2">
+        <v>370500</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" si="0"/>
+        <v>22548</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C22" s="2">
-        <v>150000</v>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="C22">
+        <v>263857</v>
+      </c>
+      <c r="D22" s="2">
+        <v>243000</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="0"/>
+        <v>20857</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C23" s="2">
-        <v>120000</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="C23">
+        <v>237804</v>
+      </c>
+      <c r="D23" s="2">
+        <v>238000</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" si="0"/>
+        <v>-196</v>
+      </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C24" s="2">
-        <v>95000</v>
-      </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="C24">
+        <v>305211</v>
+      </c>
+      <c r="D24" s="2">
+        <v>214000</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="0"/>
+        <v>91211</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C25" s="2">
-        <v>80000</v>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C25">
+        <v>137041</v>
+      </c>
+      <c r="D25" s="2">
+        <v>128000</v>
+      </c>
+      <c r="E25" s="2">
+        <f t="shared" si="0"/>
+        <v>9041</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C26" s="2">
-        <v>60000</v>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="C26">
+        <v>105742</v>
+      </c>
+      <c r="D26" s="2">
+        <v>81000</v>
+      </c>
+      <c r="E26" s="2">
+        <f t="shared" si="0"/>
+        <v>24742</v>
+      </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" s="2">
-        <v>660</v>
-      </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="C27">
+        <v>40114</v>
+      </c>
+      <c r="D27" s="2">
+        <v>36000</v>
+      </c>
+      <c r="E27" s="2">
+        <f t="shared" si="0"/>
+        <v>4114</v>
+      </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C28" s="2">
-        <v>761</v>
+        <v>159</v>
+      </c>
+      <c r="C28">
+        <v>77660</v>
       </c>
       <c r="D28" s="2">
-        <v>660</v>
-      </c>
-      <c r="E28" s="2"/>
+        <v>13000</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" si="0"/>
+        <v>64660</v>
+      </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C29" s="2">
-        <v>892</v>
+        <v>160</v>
+      </c>
+      <c r="C29">
+        <v>5947</v>
       </c>
       <c r="D29" s="2">
-        <v>761</v>
-      </c>
-      <c r="E29" s="2"/>
+        <v>5200</v>
+      </c>
+      <c r="E29" s="2">
+        <f t="shared" si="0"/>
+        <v>747</v>
+      </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C30" s="2">
-        <v>1064</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="C30">
+        <v>981</v>
+      </c>
+      <c r="D30" s="2">
+        <v>980</v>
+      </c>
+      <c r="E30" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C31" s="2">
-        <v>444</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="C31">
+        <v>89</v>
+      </c>
+      <c r="D31" s="2">
+        <v>70</v>
+      </c>
+      <c r="E31" s="2">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C32" s="2">
-        <v>169</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+        <v>660</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="C33" s="2">
-        <v>92</v>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+        <v>761</v>
+      </c>
+      <c r="D33" s="2">
+        <v>660</v>
+      </c>
+      <c r="E33" s="2">
+        <f t="shared" si="0"/>
+        <v>101</v>
+      </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="C34" s="2">
-        <v>78</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+        <v>1206</v>
+      </c>
+      <c r="D34" s="2">
+        <v>761</v>
+      </c>
+      <c r="E34" s="2">
+        <f t="shared" si="0"/>
+        <v>445</v>
+      </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="C35" s="2">
-        <v>66</v>
-      </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
+        <v>1016</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1206</v>
+      </c>
+      <c r="E35" s="2">
+        <f t="shared" si="0"/>
+        <v>-190</v>
+      </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C36" s="2">
-        <v>56</v>
-      </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1016</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="0"/>
+        <v>-594</v>
+      </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C37" s="2">
-        <v>32</v>
-      </c>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="C37">
+        <v>1960</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1064</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="0"/>
+        <v>896</v>
+      </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C38" s="2">
-        <v>31</v>
-      </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="C38">
+        <v>771</v>
+      </c>
+      <c r="D38" s="2">
+        <v>444</v>
+      </c>
+      <c r="E38" s="2">
+        <f t="shared" si="0"/>
+        <v>327</v>
+      </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C39" s="2">
-        <v>28</v>
-      </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="C39">
+        <v>250</v>
+      </c>
+      <c r="D39" s="2">
+        <v>169</v>
+      </c>
+      <c r="E39" s="2">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C40" s="2">
-        <v>27</v>
-      </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="C40">
+        <v>150</v>
+      </c>
+      <c r="D40" s="2">
+        <v>92</v>
+      </c>
+      <c r="E40" s="2">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C41" s="2">
-        <v>823</v>
-      </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="C41">
+        <v>122</v>
+      </c>
+      <c r="D41" s="2">
+        <v>73</v>
+      </c>
+      <c r="E41" s="2">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C42" s="2">
-        <v>557</v>
+        <v>168</v>
+      </c>
+      <c r="C42">
+        <v>105</v>
       </c>
       <c r="D42" s="2">
-        <v>823</v>
-      </c>
-      <c r="E42" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="E42" s="2">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43">
+        <v>95</v>
+      </c>
+      <c r="D43" s="2">
+        <v>56</v>
+      </c>
+      <c r="E43" s="2">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C44">
+        <v>51</v>
+      </c>
+      <c r="D44" s="2">
+        <v>34</v>
+      </c>
+      <c r="E44" s="2">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C45">
+        <v>55</v>
+      </c>
+      <c r="D45" s="2">
+        <v>32</v>
+      </c>
+      <c r="E45" s="2">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C46">
+        <v>52</v>
+      </c>
+      <c r="D46" s="2">
+        <v>31</v>
+      </c>
+      <c r="E46" s="2">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C47">
+        <v>50</v>
+      </c>
+      <c r="D47" s="2">
+        <v>28</v>
+      </c>
+      <c r="E47" s="2">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48">
+        <v>50</v>
+      </c>
+      <c r="D48" s="2">
+        <v>27</v>
+      </c>
+      <c r="E48" s="2">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B49" s="7">
+        <v>46023</v>
+      </c>
+      <c r="C49" s="2">
+        <v>823</v>
+      </c>
+      <c r="D49" s="2">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2">
+        <f t="shared" si="0"/>
+        <v>823</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" s="7">
+        <v>46054</v>
+      </c>
+      <c r="C50" s="2">
+        <v>557</v>
+      </c>
+      <c r="D50" s="2">
+        <v>823</v>
+      </c>
+      <c r="E50" s="2">
+        <f t="shared" si="0"/>
+        <v>-266</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B51" s="7">
+        <v>46082</v>
+      </c>
+      <c r="C51" s="2">
+        <v>469</v>
+      </c>
+      <c r="D51" s="2">
+        <v>557</v>
+      </c>
+      <c r="E51" s="2">
+        <f t="shared" si="0"/>
+        <v>-88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="7">
+        <v>46113</v>
+      </c>
+      <c r="C52" s="2">
+        <v>85</v>
+      </c>
+      <c r="D52" s="2">
+        <v>469</v>
+      </c>
+      <c r="E52" s="2">
+        <f t="shared" si="0"/>
+        <v>-384</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="7">
+        <v>46143</v>
+      </c>
+      <c r="C53" s="2">
+        <v>363</v>
+      </c>
+      <c r="D53" s="2">
+        <v>85</v>
+      </c>
+      <c r="E53" s="2">
+        <f t="shared" si="0"/>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C43" s="2">
-        <v>223</v>
-      </c>
-      <c r="D43" s="2">
-        <v>557</v>
-      </c>
-      <c r="E43" s="2"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B54" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
